--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_10d/rsi_10_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_backtest_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_10d/rsi_10_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_backtest_metrics.xlsx
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.9270564403284813</v>
+        <v>0.8964014772228963</v>
       </c>
     </row>
     <row r="6">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>-0.07294355967151134</v>
+        <v>-0.1035985227771099</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-0.01424841091605211</v>
+        <v>-0.02050891910229058</v>
       </c>
     </row>
     <row r="8">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.002627755531353415</v>
+        <v>-0.003739933185317845</v>
       </c>
     </row>
     <row r="10">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.2932923333282434</v>
+        <v>0.2112603965363017</v>
       </c>
     </row>
     <row r="11">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.04697913026706223</v>
+        <v>-0.0628981937384526</v>
       </c>
     </row>
     <row r="12">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.06724912819073615</v>
+        <v>-0.08867366651511387</v>
       </c>
     </row>
     <row r="13">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.5693352558374578</v>
+        <v>0.4681323527168623</v>
       </c>
     </row>
     <row r="14">
@@ -699,7 +699,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2021年09月-2025年06月</t>
+          <t>2021年09月-2024年09月</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.02502639836539467</v>
+        <v>-0.04381008700480667</v>
       </c>
     </row>
     <row r="16">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.2453688456863157</v>
+        <v>0.188703388426873</v>
       </c>
     </row>
     <row r="17">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.1113855394278187</v>
+        <v>0.001399154267401974</v>
       </c>
     </row>
     <row r="18">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.430636117985058</v>
+        <v>0.3460238995118793</v>
       </c>
     </row>
     <row r="19">
@@ -776,7 +776,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2021年09月-2025年07月</t>
+          <t>2021年09月-2025年10月</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>17.30734372446259</v>
+        <v>12.86996373501649</v>
       </c>
     </row>
     <row r="21">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.06920023795555327</v>
+        <v>0.05145818833445155</v>
       </c>
     </row>
     <row r="22">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.1678184471649947</v>
+        <v>0.1278974986890594</v>
       </c>
     </row>
     <row r="23">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>2.654135338345865</v>
+        <v>3.204511278195489</v>
       </c>
     </row>
     <row r="24">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
